--- a/resources/templates/standard/J3100-01.xlsx
+++ b/resources/templates/standard/J3100-01.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>변경구분</t>
   </si>
@@ -774,24 +777,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J1" s="2"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
@@ -805,7 +810,7 @@
       <c r="W1" s="4"/>
       <c r="X1" s="4"/>
       <c r="Y1" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
@@ -827,7 +832,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J2" s="5"/>
       <c r="K2" s="6"/>
@@ -845,27 +850,27 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5"/>
       <c r="AC2" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD2" s="5"/>
       <c r="AE2" s="5"/>
       <c r="AF2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG2" s="5"/>
       <c r="AH2" s="5"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8"/>
@@ -875,7 +880,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -885,7 +890,7 @@
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
@@ -907,7 +912,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
@@ -921,7 +926,7 @@
       <c r="K4" s="10"/>
       <c r="L4" s="10"/>
       <c r="M4" s="11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N4" s="11"/>
       <c r="O4" s="11"/>
@@ -947,7 +952,7 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="12"/>
       <c r="C5" s="12"/>
@@ -985,10 +990,10 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -1134,7 +1139,7 @@
     <row r="10" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
       <c r="B10" s="15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
@@ -1280,7 +1285,7 @@
     <row r="14" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>
       <c r="B14" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -1291,7 +1296,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
@@ -1302,7 +1307,7 @@
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U14" s="5"/>
       <c r="V14" s="5"/>
@@ -1313,7 +1318,7 @@
       <c r="AA14" s="5"/>
       <c r="AB14" s="5"/>
       <c r="AC14" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD14" s="5"/>
       <c r="AE14" s="5"/>
@@ -1431,10 +1436,10 @@
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1448,14 +1453,14 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
       <c r="S18" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
@@ -1463,7 +1468,7 @@
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z18" s="2"/>
       <c r="AA18" s="2"/>
@@ -1478,7 +1483,7 @@
     <row r="19" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>
       <c r="B19" s="16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -1503,7 +1508,7 @@
       <c r="W19" s="17"/>
       <c r="X19" s="17"/>
       <c r="Y19" s="18" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z19" s="18"/>
       <c r="AA19" s="18"/>
@@ -1518,7 +1523,7 @@
     <row r="20" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>
       <c r="B20" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="19"/>
       <c r="D20" s="19"/>
@@ -1556,7 +1561,7 @@
     <row r="21" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>
       <c r="B21" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
@@ -1594,7 +1599,7 @@
     <row r="22" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
       <c r="B22" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -1632,7 +1637,7 @@
     <row r="23" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="13"/>
       <c r="B23" s="21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" s="21"/>
       <c r="D23" s="21"/>
@@ -1705,14 +1710,14 @@
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="24"/>
       <c r="C25" s="24"/>
       <c r="D25" s="24"/>
       <c r="E25" s="24"/>
       <c r="F25" s="25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
@@ -1733,20 +1738,20 @@
       <c r="W25" s="25"/>
       <c r="X25" s="25"/>
       <c r="Y25" s="26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA25" s="2"/>
       <c r="AB25" s="2"/>
       <c r="AC25" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD25" s="2"/>
       <c r="AE25" s="2"/>
       <c r="AF25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG25" s="2"/>
       <c r="AH25" s="2"/>
@@ -1825,43 +1830,43 @@
     </row>
     <row r="28" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
       <c r="D28" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
       <c r="Q28" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
       <c r="T28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U28" s="6"/>
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
       <c r="X28" s="6"/>
       <c r="Y28" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Z28" s="5"/>
       <c r="AA28" s="5"/>
@@ -1875,10 +1880,10 @@
     </row>
     <row r="29" ht="18" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29" s="28"/>
@@ -1898,14 +1903,14 @@
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
       <c r="T29" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U29" s="5"/>
       <c r="V29" s="5"/>
       <c r="W29" s="6"/>
       <c r="X29" s="6"/>
       <c r="Y29" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z29" s="5"/>
       <c r="AA29" s="5"/>
@@ -1914,7 +1919,7 @@
       <c r="AD29" s="5"/>
       <c r="AE29" s="5"/>
       <c r="AF29" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AG29" s="5"/>
       <c r="AH29" s="5"/>
@@ -1945,7 +1950,7 @@
       <c r="W30" s="6"/>
       <c r="X30" s="6"/>
       <c r="Y30" s="29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z30" s="29"/>
       <c r="AA30" s="29"/>
@@ -1983,7 +1988,7 @@
       <c r="W31" s="6"/>
       <c r="X31" s="6"/>
       <c r="Y31" s="29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z31" s="29"/>
       <c r="AA31" s="29"/>
@@ -2016,14 +2021,14 @@
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
       <c r="T32" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U32" s="7"/>
       <c r="V32" s="7"/>
       <c r="W32" s="6"/>
       <c r="X32" s="6"/>
       <c r="Y32" s="29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z32" s="29"/>
       <c r="AA32" s="29"/>
@@ -2061,7 +2066,7 @@
       <c r="W33" s="6"/>
       <c r="X33" s="6"/>
       <c r="Y33" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z33" s="29"/>
       <c r="AA33" s="29"/>
@@ -2099,7 +2104,7 @@
       <c r="W34" s="6"/>
       <c r="X34" s="6"/>
       <c r="Y34" s="29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Z34" s="29"/>
       <c r="AA34" s="29"/>
@@ -2132,14 +2137,14 @@
       <c r="R35" s="28"/>
       <c r="S35" s="28"/>
       <c r="T35" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U35" s="5"/>
       <c r="V35" s="5"/>
       <c r="W35" s="6"/>
       <c r="X35" s="6"/>
       <c r="Y35" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z35" s="29"/>
       <c r="AA35" s="29"/>
@@ -2177,7 +2182,7 @@
       <c r="W36" s="6"/>
       <c r="X36" s="6"/>
       <c r="Y36" s="29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z36" s="29"/>
       <c r="AA36" s="29"/>
@@ -2246,7 +2251,7 @@
       <c r="R38" s="28"/>
       <c r="S38" s="28"/>
       <c r="T38" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U38" s="5"/>
       <c r="V38" s="5"/>
